--- a/fhir/StructureDefinition-ehealth-patient.xlsx
+++ b/fhir/StructureDefinition-ehealth-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5890" uniqueCount="831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5890" uniqueCount="828">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1539,19 +1539,10 @@
     <t>Patient.address:officialHomeAddress.extension:municipalityCode</t>
   </si>
   <si>
-    <t>Danish Core Municipality codes</t>
-  </si>
-  <si>
     <t>Patient.address:officialHomeAddress.extension:regionalSubDivisionCodes</t>
   </si>
   <si>
-    <t>Danish Core Regional Sub Division Codes Extension</t>
-  </si>
-  <si>
     <t>Patient.address:officialHomeAddress.extension:address-official</t>
-  </si>
-  <si>
-    <t>Official Address</t>
   </si>
   <si>
     <t>Patient.address:officialHomeAddress.use</t>
@@ -1811,7 +1802,13 @@
     <t>municipalityCodes</t>
   </si>
   <si>
+    <t>Danish Core Municipality codes</t>
+  </si>
+  <si>
     <t>Patient.contact.address.extension:regionalSubDivisionCodes</t>
+  </si>
+  <si>
+    <t>Danish Core Regional Sub Division Codes Extension</t>
   </si>
   <si>
     <t>Patient.contact.address.use</t>
@@ -2318,9 +2315,6 @@
     <t>Patient.generalPractitioner:YderNummer.type</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
-  </si>
-  <si>
     <t>Patient.generalPractitioner:YderNummer.identifier</t>
   </si>
   <si>
@@ -2387,7 +2381,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -2414,7 +2408,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid.1.2.208.176.1.4</t>
+    <t>urn:oid:1.2.208.176.1.4</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -2481,10 +2475,6 @@
   </si>
   <si>
     <t>Patient.generalPractitioner.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
   </si>
   <si>
     <t>Organization that issued id (may be just text)</t>
@@ -11057,7 +11047,7 @@
         <v>393</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>490</v>
+        <v>394</v>
       </c>
       <c r="M70" t="s" s="2">
         <v>395</v>
@@ -11143,7 +11133,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>390</v>
@@ -11174,7 +11164,7 @@
         <v>398</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>492</v>
+        <v>399</v>
       </c>
       <c r="M71" t="s" s="2">
         <v>400</v>
@@ -11260,7 +11250,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>390</v>
@@ -11291,7 +11281,7 @@
         <v>403</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>494</v>
+        <v>404</v>
       </c>
       <c r="M72" t="s" s="2">
         <v>405</v>
@@ -11377,7 +11367,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>406</v>
@@ -11496,7 +11486,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>416</v>
@@ -11613,7 +11603,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>425</v>
@@ -11732,7 +11722,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>432</v>
@@ -11847,7 +11837,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>439</v>
@@ -11962,7 +11952,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>447</v>
@@ -12079,7 +12069,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>456</v>
@@ -12194,7 +12184,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>463</v>
@@ -12309,7 +12299,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>471</v>
@@ -12426,7 +12416,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>478</v>
@@ -12543,10 +12533,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12569,17 +12559,17 @@
         <v>79</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>79</v>
@@ -12604,11 +12594,11 @@
         <v>79</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>79</v>
@@ -12626,7 +12616,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
@@ -12641,16 +12631,16 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>79</v>
@@ -12658,10 +12648,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12684,19 +12674,19 @@
         <v>79</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>79</v>
@@ -12745,7 +12735,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
@@ -12760,7 +12750,7 @@
         <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>196</v>
@@ -12769,7 +12759,7 @@
         <v>79</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>79</v>
@@ -12777,10 +12767,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12803,19 +12793,19 @@
         <v>79</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="N85" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>79</v>
@@ -12864,7 +12854,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
@@ -12879,7 +12869,7 @@
         <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>196</v>
@@ -12888,7 +12878,7 @@
         <v>79</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>79</v>
@@ -12896,10 +12886,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12922,19 +12912,19 @@
         <v>79</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N86" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>79</v>
@@ -12983,7 +12973,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
@@ -12995,10 +12985,10 @@
         <v>79</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>196</v>
@@ -13015,10 +13005,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13130,10 +13120,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13243,13 +13233,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>79</v>
@@ -13271,13 +13261,13 @@
         <v>79</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13360,14 +13350,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13389,10 +13379,10 @@
         <v>132</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>163</v>
@@ -13447,7 +13437,7 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>77</v>
@@ -13479,10 +13469,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13505,17 +13495,17 @@
         <v>79</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
@@ -13540,11 +13530,11 @@
         <v>79</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>79</v>
@@ -13562,7 +13552,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>77</v>
@@ -13577,7 +13567,7 @@
         <v>99</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>196</v>
@@ -13586,7 +13576,7 @@
         <v>79</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>79</v>
@@ -13594,10 +13584,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13623,14 +13613,14 @@
         <v>199</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>79</v>
@@ -13679,7 +13669,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>77</v>
@@ -13703,7 +13693,7 @@
         <v>79</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>79</v>
@@ -13711,10 +13701,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13740,13 +13730,13 @@
         <v>286</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="O93" t="s" s="2">
         <v>290</v>
@@ -13798,7 +13788,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>77</v>
@@ -13822,7 +13812,7 @@
         <v>79</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>79</v>
@@ -13830,10 +13820,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13859,14 +13849,14 @@
         <v>381</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>79</v>
@@ -13915,7 +13905,7 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>77</v>
@@ -13939,7 +13929,7 @@
         <v>79</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>79</v>
@@ -13947,10 +13937,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14062,10 +14052,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14179,13 +14169,13 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>79</v>
@@ -14210,7 +14200,7 @@
         <v>393</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>490</v>
+        <v>574</v>
       </c>
       <c r="M97" t="s" s="2">
         <v>395</v>
@@ -14296,10 +14286,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="C98" t="s" s="2">
         <v>397</v>
@@ -14327,7 +14317,7 @@
         <v>398</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>492</v>
+        <v>576</v>
       </c>
       <c r="M98" t="s" s="2">
         <v>400</v>
@@ -14413,10 +14403,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14532,10 +14522,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14649,10 +14639,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14768,10 +14758,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14883,10 +14873,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14998,10 +14988,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15115,10 +15105,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15230,10 +15220,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15345,10 +15335,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15462,10 +15452,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15579,10 +15569,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15611,11 +15601,11 @@
         <v>353</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>79</v>
@@ -15664,7 +15654,7 @@
         <v>79</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>77</v>
@@ -15688,7 +15678,7 @@
         <v>79</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>79</v>
@@ -15696,10 +15686,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15722,17 +15712,17 @@
         <v>79</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="L110" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="M110" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>79</v>
@@ -15781,7 +15771,7 @@
         <v>79</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>77</v>
@@ -15790,13 +15780,13 @@
         <v>87</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>196</v>
@@ -15805,7 +15795,7 @@
         <v>79</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>79</v>
@@ -15813,10 +15803,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15842,10 +15832,10 @@
         <v>278</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15896,7 +15886,7 @@
         <v>79</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>77</v>
@@ -15911,7 +15901,7 @@
         <v>99</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>196</v>
@@ -15928,10 +15918,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15954,19 +15944,19 @@
         <v>79</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="N112" t="s" s="2">
+      <c r="O112" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>79</v>
@@ -16015,7 +16005,7 @@
         <v>79</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>77</v>
@@ -16030,10 +16020,10 @@
         <v>99</v>
       </c>
       <c r="AK112" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AL112" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>79</v>
@@ -16047,10 +16037,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16162,10 +16152,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16279,14 +16269,14 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -16308,10 +16298,10 @@
         <v>132</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="N115" t="s" s="2">
         <v>163</v>
@@ -16366,7 +16356,7 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>77</v>
@@ -16398,10 +16388,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16424,19 +16414,19 @@
         <v>79</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="N116" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="N116" t="s" s="2">
+      <c r="O116" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>79</v>
@@ -16485,7 +16475,7 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>87</v>
@@ -16500,16 +16490,16 @@
         <v>99</v>
       </c>
       <c r="AK116" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AL116" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="AL116" t="s" s="2">
+      <c r="AM116" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN116" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>79</v>
@@ -16517,10 +16507,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16632,10 +16622,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16749,10 +16739,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16775,19 +16765,19 @@
         <v>88</v>
       </c>
       <c r="K119" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="L119" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="L119" t="s" s="2">
+      <c r="M119" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="N119" t="s" s="2">
+      <c r="O119" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>79</v>
@@ -16836,7 +16826,7 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>77</v>
@@ -16851,16 +16841,16 @@
         <v>99</v>
       </c>
       <c r="AK119" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN119" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>79</v>
@@ -16868,10 +16858,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16983,10 +16973,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17100,10 +17090,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17129,65 +17119,65 @@
         <v>101</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="N122" t="s" s="2">
+      <c r="O122" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF122" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>77</v>
@@ -17202,16 +17192,16 @@
         <v>99</v>
       </c>
       <c r="AK122" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN122" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>79</v>
@@ -17219,10 +17209,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17248,13 +17238,13 @@
         <v>213</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -17304,7 +17294,7 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>77</v>
@@ -17319,16 +17309,16 @@
         <v>99</v>
       </c>
       <c r="AK123" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN123" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>79</v>
@@ -17336,10 +17326,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17365,14 +17355,14 @@
         <v>107</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>79</v>
@@ -17421,7 +17411,7 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>77</v>
@@ -17436,16 +17426,16 @@
         <v>99</v>
       </c>
       <c r="AK124" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN124" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>79</v>
@@ -17453,10 +17443,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17482,14 +17472,14 @@
         <v>213</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>79</v>
@@ -17538,7 +17528,7 @@
         <v>79</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>77</v>
@@ -17553,16 +17543,16 @@
         <v>99</v>
       </c>
       <c r="AK125" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN125" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>664</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>79</v>
@@ -17570,10 +17560,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17599,16 +17589,16 @@
         <v>189</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="N126" t="s" s="2">
+      <c r="O126" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>79</v>
@@ -17657,7 +17647,7 @@
         <v>79</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>77</v>
@@ -17672,16 +17662,16 @@
         <v>99</v>
       </c>
       <c r="AK126" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN126" t="s" s="2">
         <v>671</v>
-      </c>
-      <c r="AL126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN126" t="s" s="2">
-        <v>672</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>79</v>
@@ -17689,10 +17679,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17718,16 +17708,16 @@
         <v>213</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>674</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>675</v>
       </c>
-      <c r="N127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>79</v>
@@ -17776,7 +17766,7 @@
         <v>79</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>77</v>
@@ -17791,16 +17781,16 @@
         <v>99</v>
       </c>
       <c r="AK127" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN127" t="s" s="2">
         <v>679</v>
-      </c>
-      <c r="AL127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN127" t="s" s="2">
-        <v>680</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>79</v>
@@ -17808,10 +17798,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17837,16 +17827,16 @@
         <v>189</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>682</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>683</v>
       </c>
-      <c r="N128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>79</v>
@@ -17895,7 +17885,7 @@
         <v>79</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>77</v>
@@ -17910,16 +17900,16 @@
         <v>99</v>
       </c>
       <c r="AK128" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="AL128" t="s" s="2">
         <v>686</v>
       </c>
-      <c r="AL128" t="s" s="2">
+      <c r="AM128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN128" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN128" t="s" s="2">
-        <v>688</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>79</v>
@@ -17927,14 +17917,14 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -17953,16 +17943,16 @@
         <v>79</v>
       </c>
       <c r="K129" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="L129" t="s" s="2">
         <v>691</v>
       </c>
-      <c r="L129" t="s" s="2">
+      <c r="M129" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="M129" t="s" s="2">
+      <c r="N129" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -18000,7 +17990,7 @@
         <v>79</v>
       </c>
       <c r="AB129" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="AC129" s="2"/>
       <c r="AD129" t="s" s="2">
@@ -18010,7 +18000,7 @@
         <v>136</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>77</v>
@@ -18025,7 +18015,7 @@
         <v>99</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>196</v>
@@ -18034,7 +18024,7 @@
         <v>79</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>79</v>
@@ -18042,16 +18032,16 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="C130" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="B130" t="s" s="2">
+      <c r="D130" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="C130" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="D130" t="s" s="2">
-        <v>690</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -18070,16 +18060,16 @@
         <v>79</v>
       </c>
       <c r="K130" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="L130" t="s" s="2">
         <v>700</v>
       </c>
-      <c r="L130" t="s" s="2">
-        <v>701</v>
-      </c>
       <c r="M130" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="N130" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -18129,7 +18119,7 @@
         <v>79</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>77</v>
@@ -18144,7 +18134,7 @@
         <v>99</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>196</v>
@@ -18153,7 +18143,7 @@
         <v>79</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>79</v>
@@ -18161,10 +18151,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="B131" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18276,10 +18266,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="B132" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18393,10 +18383,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="B133" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18422,13 +18412,13 @@
         <v>213</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>708</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>709</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>710</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18478,16 +18468,16 @@
         <v>79</v>
       </c>
       <c r="AF133" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI133" t="s" s="2">
         <v>711</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>712</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>99</v>
@@ -18510,10 +18500,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="B134" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18539,13 +18529,13 @@
         <v>101</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>715</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>716</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -18571,31 +18561,31 @@
         <v>79</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="Y134" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="Z134" t="s" s="2">
         <v>718</v>
       </c>
-      <c r="Z134" t="s" s="2">
+      <c r="AA134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF134" t="s" s="2">
         <v>719</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>720</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>77</v>
@@ -18627,10 +18617,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="B135" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>722</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18653,16 +18643,16 @@
         <v>88</v>
       </c>
       <c r="K135" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="L135" t="s" s="2">
         <v>723</v>
       </c>
-      <c r="L135" t="s" s="2">
+      <c r="M135" t="s" s="2">
         <v>724</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>725</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>726</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18712,7 +18702,7 @@
         <v>79</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>77</v>
@@ -18727,7 +18717,7 @@
         <v>99</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>79</v>
@@ -18744,10 +18734,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="B136" t="s" s="2">
         <v>729</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>730</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18773,13 +18763,13 @@
         <v>213</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>731</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>732</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>733</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -18829,7 +18819,7 @@
         <v>79</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>77</v>
@@ -18861,16 +18851,16 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="C137" t="s" s="2">
         <v>735</v>
       </c>
-      <c r="B137" t="s" s="2">
+      <c r="D137" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="C137" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="D137" t="s" s="2">
-        <v>690</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
@@ -18889,16 +18879,16 @@
         <v>79</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L137" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="M137" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="M137" t="s" s="2">
+      <c r="N137" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -18948,7 +18938,7 @@
         <v>79</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>77</v>
@@ -18963,7 +18953,7 @@
         <v>99</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>196</v>
@@ -18972,7 +18962,7 @@
         <v>79</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>79</v>
@@ -18980,10 +18970,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19095,10 +19085,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19212,10 +19202,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19241,13 +19231,13 @@
         <v>213</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>708</v>
       </c>
-      <c r="M140" t="s" s="2">
+      <c r="N140" t="s" s="2">
         <v>709</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>710</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -19297,16 +19287,16 @@
         <v>79</v>
       </c>
       <c r="AF140" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI140" t="s" s="2">
         <v>711</v>
-      </c>
-      <c r="AG140" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH140" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI140" t="s" s="2">
-        <v>712</v>
       </c>
       <c r="AJ140" t="s" s="2">
         <v>99</v>
@@ -19329,10 +19319,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19358,13 +19348,13 @@
         <v>101</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>715</v>
       </c>
-      <c r="M141" t="s" s="2">
+      <c r="N141" t="s" s="2">
         <v>716</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19390,14 +19380,14 @@
         <v>79</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="Y141" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="Z141" t="s" s="2">
         <v>718</v>
       </c>
-      <c r="Z141" t="s" s="2">
-        <v>741</v>
-      </c>
       <c r="AA141" t="s" s="2">
         <v>79</v>
       </c>
@@ -19414,7 +19404,7 @@
         <v>79</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>77</v>
@@ -19446,10 +19436,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19475,13 +19465,13 @@
         <v>167</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>724</v>
       </c>
-      <c r="M142" t="s" s="2">
+      <c r="N142" t="s" s="2">
         <v>725</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>726</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -19531,7 +19521,7 @@
         <v>79</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>77</v>
@@ -19546,7 +19536,7 @@
         <v>99</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>79</v>
@@ -19563,10 +19553,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19678,10 +19668,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19795,10 +19785,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19824,16 +19814,16 @@
         <v>107</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="N145" t="s" s="2">
         <v>749</v>
       </c>
-      <c r="M145" t="s" s="2">
+      <c r="O145" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>752</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>79</v>
@@ -19861,28 +19851,28 @@
         <v>229</v>
       </c>
       <c r="Y145" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF145" t="s" s="2">
         <v>753</v>
-      </c>
-      <c r="Z145" t="s" s="2">
-        <v>754</v>
-      </c>
-      <c r="AA145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF145" t="s" s="2">
-        <v>755</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>77</v>
@@ -19897,7 +19887,7 @@
         <v>99</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="AL145" t="s" s="2">
         <v>79</v>
@@ -19914,10 +19904,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19940,19 +19930,19 @@
         <v>88</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="L146" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="N146" t="s" s="2">
         <v>759</v>
       </c>
-      <c r="M146" t="s" s="2">
+      <c r="O146" t="s" s="2">
         <v>760</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>761</v>
-      </c>
-      <c r="O146" t="s" s="2">
-        <v>762</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>79</v>
@@ -19977,31 +19967,31 @@
         <v>79</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="Y146" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF146" t="s" s="2">
         <v>763</v>
-      </c>
-      <c r="Z146" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="AA146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF146" t="s" s="2">
-        <v>765</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>77</v>
@@ -20016,7 +20006,7 @@
         <v>99</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>79</v>
@@ -20025,7 +20015,7 @@
         <v>79</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>79</v>
@@ -20033,10 +20023,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20062,16 +20052,16 @@
         <v>101</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="N147" t="s" s="2">
         <v>769</v>
       </c>
-      <c r="M147" t="s" s="2">
+      <c r="O147" t="s" s="2">
         <v>770</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>771</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>772</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>79</v>
@@ -20081,46 +20071,46 @@
         <v>79</v>
       </c>
       <c r="S147" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF147" t="s" s="2">
         <v>773</v>
-      </c>
-      <c r="T147" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="U147" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V147" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W147" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X147" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y147" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z147" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA147" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB147" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC147" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD147" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE147" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF147" t="s" s="2">
-        <v>775</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>77</v>
@@ -20135,7 +20125,7 @@
         <v>99</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>79</v>
@@ -20144,7 +20134,7 @@
         <v>79</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>79</v>
@@ -20152,10 +20142,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20181,13 +20171,13 @@
         <v>213</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="N148" t="s" s="2">
         <v>780</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>782</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -20201,7 +20191,7 @@
         <v>79</v>
       </c>
       <c r="T148" t="s" s="2">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="U148" t="s" s="2">
         <v>79</v>
@@ -20237,7 +20227,7 @@
         <v>79</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>77</v>
@@ -20252,7 +20242,7 @@
         <v>99</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="AL148" t="s" s="2">
         <v>79</v>
@@ -20261,7 +20251,7 @@
         <v>79</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>79</v>
@@ -20269,10 +20259,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20298,10 +20288,10 @@
         <v>278</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -20352,7 +20342,7 @@
         <v>79</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>77</v>
@@ -20367,7 +20357,7 @@
         <v>99</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="AL149" t="s" s="2">
         <v>79</v>
@@ -20376,7 +20366,7 @@
         <v>79</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>79</v>
@@ -20384,10 +20374,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20410,16 +20400,16 @@
         <v>88</v>
       </c>
       <c r="K150" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="L150" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="M150" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="N150" t="s" s="2">
         <v>796</v>
-      </c>
-      <c r="L150" t="s" s="2">
-        <v>797</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>798</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>799</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20469,7 +20459,7 @@
         <v>79</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>77</v>
@@ -20484,7 +20474,7 @@
         <v>99</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="AL150" t="s" s="2">
         <v>79</v>
@@ -20493,7 +20483,7 @@
         <v>79</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>79</v>
@@ -20501,10 +20491,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20530,13 +20520,13 @@
         <v>213</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="M151" t="s" s="2">
         <v>731</v>
       </c>
-      <c r="M151" t="s" s="2">
+      <c r="N151" t="s" s="2">
         <v>732</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>733</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20586,7 +20576,7 @@
         <v>79</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>77</v>
@@ -20618,10 +20608,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20644,19 +20634,19 @@
         <v>88</v>
       </c>
       <c r="K152" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="L152" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="M152" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="N152" t="s" s="2">
         <v>805</v>
       </c>
-      <c r="L152" t="s" s="2">
+      <c r="O152" t="s" s="2">
         <v>806</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>807</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>808</v>
-      </c>
-      <c r="O152" t="s" s="2">
-        <v>809</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>79</v>
@@ -20705,7 +20695,7 @@
         <v>79</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>77</v>
@@ -20720,10 +20710,10 @@
         <v>99</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>79</v>
@@ -20737,10 +20727,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20763,19 +20753,19 @@
         <v>88</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="M153" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="O153" t="s" s="2">
         <v>812</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>814</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>815</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>79</v>
@@ -20824,7 +20814,7 @@
         <v>79</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>77</v>
@@ -20839,7 +20829,7 @@
         <v>99</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="AL153" t="s" s="2">
         <v>196</v>
@@ -20856,10 +20846,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20971,10 +20961,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21088,14 +21078,14 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -21117,10 +21107,10 @@
         <v>132</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="N156" t="s" s="2">
         <v>163</v>
@@ -21175,7 +21165,7 @@
         <v>79</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>77</v>
@@ -21207,10 +21197,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21233,16 +21223,16 @@
         <v>88</v>
       </c>
       <c r="K157" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="L157" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="M157" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="N157" t="s" s="2">
         <v>821</v>
-      </c>
-      <c r="L157" t="s" s="2">
-        <v>822</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>823</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>824</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -21292,7 +21282,7 @@
         <v>79</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>87</v>
@@ -21316,7 +21306,7 @@
         <v>79</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>79</v>
@@ -21324,10 +21314,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21353,10 +21343,10 @@
         <v>107</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -21386,10 +21376,10 @@
         <v>229</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>79</v>
@@ -21407,7 +21397,7 @@
         <v>79</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>87</v>
@@ -21422,7 +21412,7 @@
         <v>99</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="AL158" t="s" s="2">
         <v>196</v>

--- a/fhir/StructureDefinition-ehealth-patient.xlsx
+++ b/fhir/StructureDefinition-ehealth-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-patient.xlsx
+++ b/fhir/StructureDefinition-ehealth-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-patient.xlsx
+++ b/fhir/StructureDefinition-ehealth-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5890" uniqueCount="828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5890" uniqueCount="829">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2301,6 +2301,10 @@
   </si>
   <si>
     <t>YderNummer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
+</t>
   </si>
   <si>
     <t>Patient.generalPractitioner:YderNummer.id</t>
@@ -18879,7 +18883,7 @@
         <v>79</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>699</v>
+        <v>736</v>
       </c>
       <c r="L137" t="s" s="2">
         <v>691</v>
@@ -18970,7 +18974,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>702</v>
@@ -19085,7 +19089,7 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>704</v>
@@ -19202,7 +19206,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>706</v>
@@ -19319,7 +19323,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>713</v>
@@ -19436,7 +19440,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>721</v>
@@ -19553,10 +19557,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19668,10 +19672,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19785,10 +19789,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19814,16 +19818,16 @@
         <v>107</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>79</v>
@@ -19851,10 +19855,10 @@
         <v>229</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>79</v>
@@ -19872,7 +19876,7 @@
         <v>79</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>77</v>
@@ -19887,7 +19891,7 @@
         <v>99</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AL145" t="s" s="2">
         <v>79</v>
@@ -19904,10 +19908,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19933,16 +19937,16 @@
         <v>503</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>79</v>
@@ -19970,10 +19974,10 @@
         <v>507</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>79</v>
@@ -19991,7 +19995,7 @@
         <v>79</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>77</v>
@@ -20006,7 +20010,7 @@
         <v>99</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>79</v>
@@ -20015,7 +20019,7 @@
         <v>79</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>79</v>
@@ -20023,10 +20027,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20052,16 +20056,16 @@
         <v>101</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>79</v>
@@ -20071,10 +20075,10 @@
         <v>79</v>
       </c>
       <c r="S147" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="T147" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="U147" t="s" s="2">
         <v>79</v>
@@ -20110,7 +20114,7 @@
         <v>79</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>77</v>
@@ -20125,7 +20129,7 @@
         <v>99</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>79</v>
@@ -20134,7 +20138,7 @@
         <v>79</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>79</v>
@@ -20142,10 +20146,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20171,13 +20175,13 @@
         <v>213</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -20191,7 +20195,7 @@
         <v>79</v>
       </c>
       <c r="T148" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="U148" t="s" s="2">
         <v>79</v>
@@ -20227,7 +20231,7 @@
         <v>79</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>77</v>
@@ -20242,7 +20246,7 @@
         <v>99</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AL148" t="s" s="2">
         <v>79</v>
@@ -20251,7 +20255,7 @@
         <v>79</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>79</v>
@@ -20259,10 +20263,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20288,10 +20292,10 @@
         <v>278</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -20342,7 +20346,7 @@
         <v>79</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>77</v>
@@ -20357,7 +20361,7 @@
         <v>99</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AL149" t="s" s="2">
         <v>79</v>
@@ -20366,7 +20370,7 @@
         <v>79</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>79</v>
@@ -20374,10 +20378,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20403,13 +20407,13 @@
         <v>592</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20459,7 +20463,7 @@
         <v>79</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>77</v>
@@ -20474,7 +20478,7 @@
         <v>99</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AL150" t="s" s="2">
         <v>79</v>
@@ -20483,7 +20487,7 @@
         <v>79</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>79</v>
@@ -20491,7 +20495,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>729</v>
@@ -20608,10 +20612,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20634,19 +20638,19 @@
         <v>88</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>79</v>
@@ -20695,7 +20699,7 @@
         <v>79</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>77</v>
@@ -20713,7 +20717,7 @@
         <v>597</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>79</v>
@@ -20727,10 +20731,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20756,16 +20760,16 @@
         <v>529</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>79</v>
@@ -20814,7 +20818,7 @@
         <v>79</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>77</v>
@@ -20829,7 +20833,7 @@
         <v>99</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="AL153" t="s" s="2">
         <v>196</v>
@@ -20846,10 +20850,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20961,10 +20965,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21078,10 +21082,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21197,10 +21201,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21223,16 +21227,16 @@
         <v>88</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -21282,7 +21286,7 @@
         <v>79</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>87</v>
@@ -21306,7 +21310,7 @@
         <v>79</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>79</v>
@@ -21314,10 +21318,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21343,10 +21347,10 @@
         <v>107</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -21376,10 +21380,10 @@
         <v>229</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>79</v>
@@ -21397,7 +21401,7 @@
         <v>79</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>87</v>
@@ -21412,7 +21416,7 @@
         <v>99</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AL158" t="s" s="2">
         <v>196</v>

--- a/fhir/StructureDefinition-ehealth-patient.xlsx
+++ b/fhir/StructureDefinition-ehealth-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-patient.xlsx
+++ b/fhir/StructureDefinition-ehealth-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-patient.xlsx
+++ b/fhir/StructureDefinition-ehealth-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
